--- a/public/exports-from-60/29189633.xlsx
+++ b/public/exports-from-60/29189633.xlsx
@@ -59,7 +59,7 @@
       </c>
       <c r="J1" t="inlineStr">
         <is>
-          <t xml:space="preserve">Areal (m²)</t>
+          <t xml:space="preserve">Opvarmet BBR-areal (m²)</t>
         </is>
       </c>
       <c r="K1" t="inlineStr">
@@ -9064,12 +9064,12 @@
       </c>
       <c r="K121" t="inlineStr">
         <is>
-          <t xml:space="preserve">311365266</t>
+          <t xml:space="preserve">311365267</t>
         </is>
       </c>
       <c r="L121" t="inlineStr">
         <is>
-          <t xml:space="preserve">Energi- og Bygningsrådgivning A/S</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="M121" t="inlineStr">
@@ -9139,12 +9139,12 @@
       </c>
       <c r="K122" t="inlineStr">
         <is>
-          <t xml:space="preserve">311365260</t>
+          <t xml:space="preserve">311365261</t>
         </is>
       </c>
       <c r="L122" t="inlineStr">
         <is>
-          <t xml:space="preserve">Energi- og Bygningsrådgivning A/S</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="M122" t="inlineStr">
@@ -9364,7 +9364,7 @@
       </c>
       <c r="K125" t="inlineStr">
         <is>
-          <t xml:space="preserve">311366596</t>
+          <t xml:space="preserve">311366598</t>
         </is>
       </c>
       <c r="L125" t="inlineStr">
@@ -9439,7 +9439,7 @@
       </c>
       <c r="K126" t="inlineStr">
         <is>
-          <t xml:space="preserve">311366602</t>
+          <t xml:space="preserve">311366603</t>
         </is>
       </c>
       <c r="L126" t="inlineStr">
@@ -9514,7 +9514,7 @@
       </c>
       <c r="K127" t="inlineStr">
         <is>
-          <t xml:space="preserve">311366589</t>
+          <t xml:space="preserve">311366590</t>
         </is>
       </c>
       <c r="L127" t="inlineStr">
@@ -12889,7 +12889,7 @@
       </c>
       <c r="K172" t="inlineStr">
         <is>
-          <t xml:space="preserve">311379031</t>
+          <t xml:space="preserve">311379034</t>
         </is>
       </c>
       <c r="L172" t="inlineStr">
@@ -13114,7 +13114,7 @@
       </c>
       <c r="K175" t="inlineStr">
         <is>
-          <t xml:space="preserve">311379054</t>
+          <t xml:space="preserve">311379055</t>
         </is>
       </c>
       <c r="L175" t="inlineStr">
@@ -15139,7 +15139,7 @@
       </c>
       <c r="K202" t="inlineStr">
         <is>
-          <t xml:space="preserve">311381685</t>
+          <t xml:space="preserve">311381687</t>
         </is>
       </c>
       <c r="L202" t="inlineStr">
@@ -15739,7 +15739,7 @@
       </c>
       <c r="K210" t="inlineStr">
         <is>
-          <t xml:space="preserve">311387766</t>
+          <t xml:space="preserve">311396690</t>
         </is>
       </c>
       <c r="L210" t="inlineStr">

--- a/public/exports-from-60/29189633.xlsx
+++ b/public/exports-from-60/29189633.xlsx
@@ -8989,12 +8989,12 @@
       </c>
       <c r="K120" t="inlineStr">
         <is>
-          <t xml:space="preserve">311365262</t>
+          <t xml:space="preserve">311365263</t>
         </is>
       </c>
       <c r="L120" t="inlineStr">
         <is>
-          <t xml:space="preserve">Energi- og Bygningsrådgivning A/S</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="M120" t="inlineStr">
@@ -9064,12 +9064,12 @@
       </c>
       <c r="K121" t="inlineStr">
         <is>
-          <t xml:space="preserve">311365267</t>
+          <t xml:space="preserve">311365266</t>
         </is>
       </c>
       <c r="L121" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">Energi- og Bygningsrådgivning A/S</t>
         </is>
       </c>
       <c r="M121" t="inlineStr">
@@ -9139,12 +9139,12 @@
       </c>
       <c r="K122" t="inlineStr">
         <is>
-          <t xml:space="preserve">311365261</t>
+          <t xml:space="preserve">311365260</t>
         </is>
       </c>
       <c r="L122" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">Energi- og Bygningsrådgivning A/S</t>
         </is>
       </c>
       <c r="M122" t="inlineStr">
@@ -9364,7 +9364,7 @@
       </c>
       <c r="K125" t="inlineStr">
         <is>
-          <t xml:space="preserve">311366598</t>
+          <t xml:space="preserve">311366599</t>
         </is>
       </c>
       <c r="L125" t="inlineStr">
@@ -9439,7 +9439,7 @@
       </c>
       <c r="K126" t="inlineStr">
         <is>
-          <t xml:space="preserve">311366603</t>
+          <t xml:space="preserve">311366605</t>
         </is>
       </c>
       <c r="L126" t="inlineStr">
@@ -9514,7 +9514,7 @@
       </c>
       <c r="K127" t="inlineStr">
         <is>
-          <t xml:space="preserve">311366590</t>
+          <t xml:space="preserve">311366591</t>
         </is>
       </c>
       <c r="L127" t="inlineStr">
@@ -9589,7 +9589,7 @@
       </c>
       <c r="K128" t="inlineStr">
         <is>
-          <t xml:space="preserve">311366593</t>
+          <t xml:space="preserve">311366595</t>
         </is>
       </c>
       <c r="L128" t="inlineStr">
@@ -12964,7 +12964,7 @@
       </c>
       <c r="K173" t="inlineStr">
         <is>
-          <t xml:space="preserve">311379064</t>
+          <t xml:space="preserve">311379069</t>
         </is>
       </c>
       <c r="L173" t="inlineStr">
@@ -13039,7 +13039,7 @@
       </c>
       <c r="K174" t="inlineStr">
         <is>
-          <t xml:space="preserve">311379047</t>
+          <t xml:space="preserve">311379050</t>
         </is>
       </c>
       <c r="L174" t="inlineStr">
@@ -13114,7 +13114,7 @@
       </c>
       <c r="K175" t="inlineStr">
         <is>
-          <t xml:space="preserve">311379055</t>
+          <t xml:space="preserve">311379059</t>
         </is>
       </c>
       <c r="L175" t="inlineStr">
@@ -15139,7 +15139,7 @@
       </c>
       <c r="K202" t="inlineStr">
         <is>
-          <t xml:space="preserve">311381687</t>
+          <t xml:space="preserve">311381685</t>
         </is>
       </c>
       <c r="L202" t="inlineStr">
@@ -15739,7 +15739,7 @@
       </c>
       <c r="K210" t="inlineStr">
         <is>
-          <t xml:space="preserve">311396690</t>
+          <t xml:space="preserve">311387766</t>
         </is>
       </c>
       <c r="L210" t="inlineStr">
@@ -25864,7 +25864,7 @@
       </c>
       <c r="K345" t="inlineStr">
         <is>
-          <t xml:space="preserve">311422167</t>
+          <t xml:space="preserve">311422168</t>
         </is>
       </c>
       <c r="L345" t="inlineStr">

--- a/public/exports-from-60/29189633.xlsx
+++ b/public/exports-from-60/29189633.xlsx
@@ -8989,12 +8989,12 @@
       </c>
       <c r="K120" t="inlineStr">
         <is>
-          <t xml:space="preserve">311365263</t>
+          <t xml:space="preserve">311365262</t>
         </is>
       </c>
       <c r="L120" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">Energi- og Bygningsrådgivning A/S</t>
         </is>
       </c>
       <c r="M120" t="inlineStr">
@@ -9064,12 +9064,12 @@
       </c>
       <c r="K121" t="inlineStr">
         <is>
-          <t xml:space="preserve">311365266</t>
+          <t xml:space="preserve">311365267</t>
         </is>
       </c>
       <c r="L121" t="inlineStr">
         <is>
-          <t xml:space="preserve">Energi- og Bygningsrådgivning A/S</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="M121" t="inlineStr">
@@ -9439,7 +9439,7 @@
       </c>
       <c r="K126" t="inlineStr">
         <is>
-          <t xml:space="preserve">311366605</t>
+          <t xml:space="preserve">311366603</t>
         </is>
       </c>
       <c r="L126" t="inlineStr">
@@ -9514,7 +9514,7 @@
       </c>
       <c r="K127" t="inlineStr">
         <is>
-          <t xml:space="preserve">311366591</t>
+          <t xml:space="preserve">311366589</t>
         </is>
       </c>
       <c r="L127" t="inlineStr">
@@ -25864,7 +25864,7 @@
       </c>
       <c r="K345" t="inlineStr">
         <is>
-          <t xml:space="preserve">311422168</t>
+          <t xml:space="preserve">311422167</t>
         </is>
       </c>
       <c r="L345" t="inlineStr">
